--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59B8D218-E7A3-4B16-9368-FD1C374996A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{611E6D04-39FD-4008-BAA4-3A257A306585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D1D5C6C0-3316-40A6-AE97-03DA312F448E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D25A4567-CAF9-430F-A4BD-F6E8ADAA4C2C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2465,31 +2465,31 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2022) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 38_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2023) - 42_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B9ADEB-839F-485C-A9BD-36EF5EE05FA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7D3F20-0D87-41CF-A341-8D214C6815A5}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC648D13-7808-48DA-B818-A428F7657DE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F2CFA5-1CF9-4D45-8B6A-1E4CC3C031DC}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F69ED54-6737-45A6-BF3F-69B98833DAC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03596A80-7941-4099-BEE1-B515B3A59111}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29162,7 +29162,7 @@
         <v>33</v>
       </c>
       <c r="P245">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R245" t="s">
         <v>585</v>
@@ -29215,7 +29215,7 @@
         <v>32</v>
       </c>
       <c r="P246">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R246" t="s">
         <v>585</v>
@@ -29268,7 +29268,7 @@
         <v>31</v>
       </c>
       <c r="P247">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R247" t="s">
         <v>585</v>
@@ -29321,7 +29321,7 @@
         <v>33</v>
       </c>
       <c r="P248">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R248" t="s">
         <v>585</v>
@@ -29374,7 +29374,7 @@
         <v>32</v>
       </c>
       <c r="P249">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R249" t="s">
         <v>585</v>
@@ -29427,7 +29427,7 @@
         <v>31</v>
       </c>
       <c r="P250">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R250" t="s">
         <v>585</v>
@@ -29480,7 +29480,7 @@
         <v>33</v>
       </c>
       <c r="P251">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R251" t="s">
         <v>585</v>
@@ -29533,7 +29533,7 @@
         <v>32</v>
       </c>
       <c r="P252">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R252" t="s">
         <v>585</v>
@@ -29586,7 +29586,7 @@
         <v>31</v>
       </c>
       <c r="P253">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R253" t="s">
         <v>585</v>
@@ -29639,7 +29639,7 @@
         <v>33</v>
       </c>
       <c r="P254">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R254" t="s">
         <v>585</v>
@@ -29692,7 +29692,7 @@
         <v>32</v>
       </c>
       <c r="P255">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R255" t="s">
         <v>585</v>
@@ -29745,7 +29745,7 @@
         <v>31</v>
       </c>
       <c r="P256">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R256" t="s">
         <v>585</v>
@@ -29798,7 +29798,7 @@
         <v>33</v>
       </c>
       <c r="P257">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R257" t="s">
         <v>585</v>
@@ -29851,7 +29851,7 @@
         <v>32</v>
       </c>
       <c r="P258">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R258" t="s">
         <v>585</v>
@@ -29904,7 +29904,7 @@
         <v>31</v>
       </c>
       <c r="P259">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R259" t="s">
         <v>585</v>
@@ -29957,7 +29957,7 @@
         <v>33</v>
       </c>
       <c r="P260">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R260" t="s">
         <v>585</v>
@@ -30010,7 +30010,7 @@
         <v>32</v>
       </c>
       <c r="P261">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R261" t="s">
         <v>585</v>
@@ -30063,7 +30063,7 @@
         <v>31</v>
       </c>
       <c r="P262">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R262" t="s">
         <v>585</v>
@@ -30116,7 +30116,7 @@
         <v>33</v>
       </c>
       <c r="P263">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R263" t="s">
         <v>585</v>
@@ -30169,7 +30169,7 @@
         <v>32</v>
       </c>
       <c r="P264">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R264" t="s">
         <v>585</v>
@@ -30222,7 +30222,7 @@
         <v>31</v>
       </c>
       <c r="P265">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R265" t="s">
         <v>585</v>
@@ -30275,7 +30275,7 @@
         <v>33</v>
       </c>
       <c r="P266">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R266" t="s">
         <v>585</v>
@@ -30328,7 +30328,7 @@
         <v>32</v>
       </c>
       <c r="P267">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R267" t="s">
         <v>585</v>
@@ -30381,7 +30381,7 @@
         <v>31</v>
       </c>
       <c r="P268">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R268" t="s">
         <v>585</v>
@@ -30434,7 +30434,7 @@
         <v>33</v>
       </c>
       <c r="P269">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R269" t="s">
         <v>585</v>
@@ -30487,7 +30487,7 @@
         <v>32</v>
       </c>
       <c r="P270">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R270" t="s">
         <v>585</v>
@@ -30540,7 +30540,7 @@
         <v>31</v>
       </c>
       <c r="P271">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R271" t="s">
         <v>585</v>
@@ -30593,7 +30593,7 @@
         <v>33</v>
       </c>
       <c r="P272">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R272" t="s">
         <v>585</v>
@@ -30646,7 +30646,7 @@
         <v>32</v>
       </c>
       <c r="P273">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R273" t="s">
         <v>585</v>
@@ -30699,7 +30699,7 @@
         <v>31</v>
       </c>
       <c r="P274">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R274" t="s">
         <v>585</v>
@@ -30752,7 +30752,7 @@
         <v>33</v>
       </c>
       <c r="P275">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R275" t="s">
         <v>585</v>
@@ -30805,7 +30805,7 @@
         <v>32</v>
       </c>
       <c r="P276">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R276" t="s">
         <v>585</v>
@@ -30858,7 +30858,7 @@
         <v>31</v>
       </c>
       <c r="P277">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R277" t="s">
         <v>585</v>
@@ -30911,7 +30911,7 @@
         <v>33</v>
       </c>
       <c r="P278">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R278" t="s">
         <v>585</v>
@@ -30964,7 +30964,7 @@
         <v>32</v>
       </c>
       <c r="P279">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R279" t="s">
         <v>585</v>
@@ -31017,7 +31017,7 @@
         <v>31</v>
       </c>
       <c r="P280">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R280" t="s">
         <v>585</v>
@@ -31070,7 +31070,7 @@
         <v>33</v>
       </c>
       <c r="P281">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R281" t="s">
         <v>585</v>
@@ -31123,7 +31123,7 @@
         <v>32</v>
       </c>
       <c r="P282">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R282" t="s">
         <v>585</v>
@@ -31176,7 +31176,7 @@
         <v>31</v>
       </c>
       <c r="P283">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R283" t="s">
         <v>585</v>
@@ -31229,7 +31229,7 @@
         <v>33</v>
       </c>
       <c r="P284">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R284" t="s">
         <v>585</v>
@@ -31282,7 +31282,7 @@
         <v>32</v>
       </c>
       <c r="P285">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R285" t="s">
         <v>585</v>
@@ -31335,7 +31335,7 @@
         <v>31</v>
       </c>
       <c r="P286">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R286" t="s">
         <v>585</v>
@@ -31388,7 +31388,7 @@
         <v>33</v>
       </c>
       <c r="P287">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R287" t="s">
         <v>585</v>
@@ -31441,7 +31441,7 @@
         <v>32</v>
       </c>
       <c r="P288">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R288" t="s">
         <v>585</v>
@@ -31494,7 +31494,7 @@
         <v>31</v>
       </c>
       <c r="P289">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R289" t="s">
         <v>585</v>
@@ -31506,7 +31506,7 @@
         <v>17</v>
       </c>
       <c r="U289" t="s">
-        <v>813</v>
+        <v>586</v>
       </c>
       <c r="V289" t="s">
         <v>587</v>
@@ -31518,7 +31518,7 @@
         <v>618</v>
       </c>
       <c r="Y289" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="290" spans="2:25" x14ac:dyDescent="0.45">
@@ -31547,7 +31547,7 @@
         <v>33</v>
       </c>
       <c r="P290">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R290" t="s">
         <v>585</v>
@@ -31559,7 +31559,7 @@
         <v>17</v>
       </c>
       <c r="U290" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="V290" t="s">
         <v>587</v>
@@ -31571,7 +31571,7 @@
         <v>618</v>
       </c>
       <c r="Y290" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="291" spans="2:25" x14ac:dyDescent="0.45">
@@ -31600,7 +31600,7 @@
         <v>32</v>
       </c>
       <c r="P291">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R291" t="s">
         <v>585</v>
@@ -31653,7 +31653,7 @@
         <v>31</v>
       </c>
       <c r="P292">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R292" t="s">
         <v>585</v>
@@ -31706,7 +31706,7 @@
         <v>33</v>
       </c>
       <c r="P293">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R293" t="s">
         <v>585</v>
@@ -31759,7 +31759,7 @@
         <v>32</v>
       </c>
       <c r="P294">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R294" t="s">
         <v>585</v>
@@ -31812,7 +31812,7 @@
         <v>31</v>
       </c>
       <c r="P295">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R295" t="s">
         <v>585</v>
@@ -31865,7 +31865,7 @@
         <v>33</v>
       </c>
       <c r="P296">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R296" t="s">
         <v>585</v>
@@ -31918,7 +31918,7 @@
         <v>32</v>
       </c>
       <c r="P297">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R297" t="s">
         <v>585</v>
@@ -31971,7 +31971,7 @@
         <v>31</v>
       </c>
       <c r="P298">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R298" t="s">
         <v>585</v>
@@ -32024,7 +32024,7 @@
         <v>33</v>
       </c>
       <c r="P299">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R299" t="s">
         <v>585</v>
@@ -32077,7 +32077,7 @@
         <v>32</v>
       </c>
       <c r="P300">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R300" t="s">
         <v>585</v>
@@ -32130,7 +32130,7 @@
         <v>31</v>
       </c>
       <c r="P301">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R301" t="s">
         <v>585</v>
@@ -32183,7 +32183,7 @@
         <v>33</v>
       </c>
       <c r="P302">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R302" t="s">
         <v>585</v>
@@ -32236,7 +32236,7 @@
         <v>32</v>
       </c>
       <c r="P303">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R303" t="s">
         <v>585</v>
@@ -32289,7 +32289,7 @@
         <v>31</v>
       </c>
       <c r="P304">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R304" t="s">
         <v>585</v>
@@ -32342,7 +32342,7 @@
         <v>33</v>
       </c>
       <c r="P305">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R305" t="s">
         <v>585</v>
@@ -32395,7 +32395,7 @@
         <v>32</v>
       </c>
       <c r="P306">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R306" t="s">
         <v>585</v>
@@ -32448,7 +32448,7 @@
         <v>31</v>
       </c>
       <c r="P307">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R307" t="s">
         <v>585</v>
@@ -32501,7 +32501,7 @@
         <v>33</v>
       </c>
       <c r="P308">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R308" t="s">
         <v>585</v>
@@ -32554,7 +32554,7 @@
         <v>32</v>
       </c>
       <c r="P309">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R309" t="s">
         <v>585</v>
@@ -32607,7 +32607,7 @@
         <v>31</v>
       </c>
       <c r="P310">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R310" t="s">
         <v>585</v>
@@ -32660,7 +32660,7 @@
         <v>33</v>
       </c>
       <c r="P311">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R311" t="s">
         <v>585</v>
@@ -32713,7 +32713,7 @@
         <v>32</v>
       </c>
       <c r="P312">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R312" t="s">
         <v>585</v>
@@ -32766,7 +32766,7 @@
         <v>31</v>
       </c>
       <c r="P313">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R313" t="s">
         <v>585</v>
@@ -32819,7 +32819,7 @@
         <v>33</v>
       </c>
       <c r="P314">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R314" t="s">
         <v>585</v>
@@ -32872,7 +32872,7 @@
         <v>32</v>
       </c>
       <c r="P315">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R315" t="s">
         <v>585</v>
@@ -32925,7 +32925,7 @@
         <v>31</v>
       </c>
       <c r="P316">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R316" t="s">
         <v>585</v>
@@ -32978,7 +32978,7 @@
         <v>33</v>
       </c>
       <c r="P317">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R317" t="s">
         <v>585</v>
@@ -33031,7 +33031,7 @@
         <v>32</v>
       </c>
       <c r="P318">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R318" t="s">
         <v>585</v>
@@ -33084,7 +33084,7 @@
         <v>31</v>
       </c>
       <c r="P319">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R319" t="s">
         <v>585</v>
@@ -33137,7 +33137,7 @@
         <v>33</v>
       </c>
       <c r="P320">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R320" t="s">
         <v>585</v>
@@ -33190,7 +33190,7 @@
         <v>32</v>
       </c>
       <c r="P321">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R321" t="s">
         <v>585</v>
@@ -33243,7 +33243,7 @@
         <v>31</v>
       </c>
       <c r="P322">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R322" t="s">
         <v>585</v>
@@ -33296,7 +33296,7 @@
         <v>33</v>
       </c>
       <c r="P323">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R323" t="s">
         <v>585</v>
@@ -33349,7 +33349,7 @@
         <v>32</v>
       </c>
       <c r="P324">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R324" t="s">
         <v>585</v>
@@ -33402,7 +33402,7 @@
         <v>31</v>
       </c>
       <c r="P325">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R325" t="s">
         <v>585</v>
@@ -33455,7 +33455,7 @@
         <v>33</v>
       </c>
       <c r="P326">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R326" t="s">
         <v>585</v>
@@ -33508,7 +33508,7 @@
         <v>32</v>
       </c>
       <c r="P327">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R327" t="s">
         <v>585</v>
@@ -33561,7 +33561,7 @@
         <v>31</v>
       </c>
       <c r="P328">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R328" t="s">
         <v>585</v>
@@ -33614,7 +33614,7 @@
         <v>33</v>
       </c>
       <c r="P329">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R329" t="s">
         <v>585</v>
@@ -33667,7 +33667,7 @@
         <v>32</v>
       </c>
       <c r="P330">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R330" t="s">
         <v>585</v>
@@ -33720,7 +33720,7 @@
         <v>31</v>
       </c>
       <c r="P331">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R331" t="s">
         <v>585</v>
@@ -33773,7 +33773,7 @@
         <v>33</v>
       </c>
       <c r="P332">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R332" t="s">
         <v>585</v>
@@ -33826,7 +33826,7 @@
         <v>32</v>
       </c>
       <c r="P333">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R333" t="s">
         <v>585</v>
@@ -33879,7 +33879,7 @@
         <v>31</v>
       </c>
       <c r="P334">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R334" t="s">
         <v>585</v>
@@ -33932,7 +33932,7 @@
         <v>33</v>
       </c>
       <c r="P335">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R335" t="s">
         <v>585</v>
@@ -33985,7 +33985,7 @@
         <v>32</v>
       </c>
       <c r="P336">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R336" t="s">
         <v>585</v>
@@ -34038,7 +34038,7 @@
         <v>31</v>
       </c>
       <c r="P337">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R337" t="s">
         <v>585</v>
@@ -34091,7 +34091,7 @@
         <v>33</v>
       </c>
       <c r="P338">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R338" t="s">
         <v>585</v>
@@ -34144,7 +34144,7 @@
         <v>32</v>
       </c>
       <c r="P339">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R339" t="s">
         <v>585</v>
@@ -34197,7 +34197,7 @@
         <v>31</v>
       </c>
       <c r="P340">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R340" t="s">
         <v>585</v>
@@ -34250,7 +34250,7 @@
         <v>33</v>
       </c>
       <c r="P341">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R341" t="s">
         <v>585</v>
@@ -34303,7 +34303,7 @@
         <v>32</v>
       </c>
       <c r="P342">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R342" t="s">
         <v>585</v>
@@ -34356,7 +34356,7 @@
         <v>31</v>
       </c>
       <c r="P343">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R343" t="s">
         <v>585</v>
@@ -34409,7 +34409,7 @@
         <v>33</v>
       </c>
       <c r="P344">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R344" t="s">
         <v>585</v>
@@ -34462,7 +34462,7 @@
         <v>32</v>
       </c>
       <c r="P345">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R345" t="s">
         <v>585</v>
@@ -34515,7 +34515,7 @@
         <v>31</v>
       </c>
       <c r="P346">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R346" t="s">
         <v>585</v>
@@ -34568,7 +34568,7 @@
         <v>33</v>
       </c>
       <c r="P347">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R347" t="s">
         <v>585</v>
@@ -34621,7 +34621,7 @@
         <v>32</v>
       </c>
       <c r="P348">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R348" t="s">
         <v>585</v>
@@ -34674,7 +34674,7 @@
         <v>31</v>
       </c>
       <c r="P349">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R349" t="s">
         <v>585</v>
@@ -34727,7 +34727,7 @@
         <v>33</v>
       </c>
       <c r="P350">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R350" t="s">
         <v>585</v>
@@ -34780,7 +34780,7 @@
         <v>32</v>
       </c>
       <c r="P351">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R351" t="s">
         <v>585</v>
@@ -34833,7 +34833,7 @@
         <v>31</v>
       </c>
       <c r="P352">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R352" t="s">
         <v>585</v>
@@ -34886,7 +34886,7 @@
         <v>33</v>
       </c>
       <c r="P353">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R353" t="s">
         <v>585</v>
@@ -34939,7 +34939,7 @@
         <v>32</v>
       </c>
       <c r="P354">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R354" t="s">
         <v>585</v>
@@ -34992,7 +34992,7 @@
         <v>31</v>
       </c>
       <c r="P355">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R355" t="s">
         <v>585</v>
@@ -35045,7 +35045,7 @@
         <v>33</v>
       </c>
       <c r="P356">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R356" t="s">
         <v>585</v>
@@ -35098,7 +35098,7 @@
         <v>32</v>
       </c>
       <c r="P357">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R357" t="s">
         <v>585</v>
@@ -35151,7 +35151,7 @@
         <v>31</v>
       </c>
       <c r="P358">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R358" t="s">
         <v>585</v>
@@ -35204,7 +35204,7 @@
         <v>33</v>
       </c>
       <c r="P359">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R359" t="s">
         <v>585</v>
@@ -35257,7 +35257,7 @@
         <v>32</v>
       </c>
       <c r="P360">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R360" t="s">
         <v>585</v>
@@ -35310,7 +35310,7 @@
         <v>31</v>
       </c>
       <c r="P361">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R361" t="s">
         <v>585</v>
@@ -35363,7 +35363,7 @@
         <v>33</v>
       </c>
       <c r="P362">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R362" t="s">
         <v>585</v>
@@ -35416,7 +35416,7 @@
         <v>32</v>
       </c>
       <c r="P363">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R363" t="s">
         <v>585</v>
@@ -35469,7 +35469,7 @@
         <v>31</v>
       </c>
       <c r="P364">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R364" t="s">
         <v>585</v>
@@ -35522,7 +35522,7 @@
         <v>33</v>
       </c>
       <c r="P365">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R365" t="s">
         <v>585</v>
@@ -35575,7 +35575,7 @@
         <v>32</v>
       </c>
       <c r="P366">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R366" t="s">
         <v>585</v>
@@ -35628,7 +35628,7 @@
         <v>31</v>
       </c>
       <c r="P367">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R367" t="s">
         <v>585</v>
@@ -35681,7 +35681,7 @@
         <v>33</v>
       </c>
       <c r="P368">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R368" t="s">
         <v>585</v>
@@ -35734,7 +35734,7 @@
         <v>32</v>
       </c>
       <c r="P369">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R369" t="s">
         <v>585</v>
@@ -35787,7 +35787,7 @@
         <v>31</v>
       </c>
       <c r="P370">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R370" t="s">
         <v>585</v>
@@ -35840,7 +35840,7 @@
         <v>33</v>
       </c>
       <c r="P371">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R371" t="s">
         <v>585</v>
@@ -35893,7 +35893,7 @@
         <v>32</v>
       </c>
       <c r="P372">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R372" t="s">
         <v>585</v>
@@ -35946,7 +35946,7 @@
         <v>31</v>
       </c>
       <c r="P373">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R373" t="s">
         <v>585</v>
@@ -35999,7 +35999,7 @@
         <v>33</v>
       </c>
       <c r="P374">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R374" t="s">
         <v>585</v>
@@ -36052,7 +36052,7 @@
         <v>32</v>
       </c>
       <c r="P375">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R375" t="s">
         <v>585</v>
@@ -36105,7 +36105,7 @@
         <v>31</v>
       </c>
       <c r="P376">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R376" t="s">
         <v>585</v>
@@ -36158,7 +36158,7 @@
         <v>33</v>
       </c>
       <c r="P377">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R377" t="s">
         <v>585</v>
@@ -36211,7 +36211,7 @@
         <v>32</v>
       </c>
       <c r="P378">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R378" t="s">
         <v>585</v>
@@ -36264,7 +36264,7 @@
         <v>31</v>
       </c>
       <c r="P379">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R379" t="s">
         <v>585</v>
@@ -36317,7 +36317,7 @@
         <v>33</v>
       </c>
       <c r="P380">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R380" t="s">
         <v>585</v>
@@ -36370,7 +36370,7 @@
         <v>32</v>
       </c>
       <c r="P381">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R381" t="s">
         <v>585</v>
@@ -36423,7 +36423,7 @@
         <v>31</v>
       </c>
       <c r="P382">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R382" t="s">
         <v>585</v>
@@ -36476,7 +36476,7 @@
         <v>33</v>
       </c>
       <c r="P383">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R383" t="s">
         <v>585</v>
@@ -36529,7 +36529,7 @@
         <v>32</v>
       </c>
       <c r="P384">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R384" t="s">
         <v>585</v>
@@ -36582,7 +36582,7 @@
         <v>31</v>
       </c>
       <c r="P385">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R385" t="s">
         <v>585</v>
@@ -36635,7 +36635,7 @@
         <v>33</v>
       </c>
       <c r="P386">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R386" t="s">
         <v>585</v>
@@ -36688,7 +36688,7 @@
         <v>32</v>
       </c>
       <c r="P387">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R387" t="s">
         <v>585</v>
@@ -36741,7 +36741,7 @@
         <v>31</v>
       </c>
       <c r="P388">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R388" t="s">
         <v>585</v>
@@ -36794,7 +36794,7 @@
         <v>33</v>
       </c>
       <c r="P389">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R389" t="s">
         <v>585</v>
@@ -36847,7 +36847,7 @@
         <v>32</v>
       </c>
       <c r="P390">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R390" t="s">
         <v>585</v>
@@ -36900,7 +36900,7 @@
         <v>31</v>
       </c>
       <c r="P391">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R391" t="s">
         <v>585</v>
@@ -36953,7 +36953,7 @@
         <v>33</v>
       </c>
       <c r="P392">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R392" t="s">
         <v>585</v>
@@ -37006,7 +37006,7 @@
         <v>32</v>
       </c>
       <c r="P393">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R393" t="s">
         <v>585</v>
@@ -37059,7 +37059,7 @@
         <v>31</v>
       </c>
       <c r="P394">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R394" t="s">
         <v>585</v>
@@ -37112,7 +37112,7 @@
         <v>33</v>
       </c>
       <c r="P395">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R395" t="s">
         <v>585</v>
@@ -37165,7 +37165,7 @@
         <v>32</v>
       </c>
       <c r="P396">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R396" t="s">
         <v>585</v>
@@ -37218,7 +37218,7 @@
         <v>31</v>
       </c>
       <c r="P397">
-        <v>0.11568880532804261</v>
+        <v>0.11568880532804263</v>
       </c>
       <c r="R397" t="s">
         <v>585</v>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296D110F-61A1-4871-AC53-CCAB6DA52E5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B10433E-F2C3-41F9-9CF6-919B612506CB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{611E6D04-39FD-4008-BAA4-3A257A306585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A867525D-0F8D-47A8-B81C-B78077B30AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D25A4567-CAF9-430F-A4BD-F6E8ADAA4C2C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{683AD899-34FE-461C-BFE1-AF05A258F664}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2468,12 +2468,12 @@
     <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
@@ -2486,13 +2486,13 @@
     <t>IRENA Gap - solar (2023) - 42_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Zwartowo solar farm_1 -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7D3F20-0D87-41CF-A341-8D214C6815A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9FBE2C5-F977-4037-912A-E38EF2065070}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F2CFA5-1CF9-4D45-8B6A-1E4CC3C031DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B554FDE1-8E2C-4F3C-915F-84F4ED03A47B}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03596A80-7941-4099-BEE1-B515B3A59111}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB93C33-DF9A-44FB-B7B8-7DC60AE7F8E9}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B10433E-F2C3-41F9-9CF6-919B612506CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF56D5A-1CFF-4DB8-B2A8-E292F4A80F10}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A867525D-0F8D-47A8-B81C-B78077B30AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C75F656F-D997-4EF7-AD18-DAC983DD47EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{683AD899-34FE-461C-BFE1-AF05A258F664}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DF54D25E-3258-44BF-A4AE-A2E297EDAFDC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2465,15 +2465,15 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
@@ -2486,13 +2486,13 @@
     <t>IRENA Gap - solar (2023) - 42_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Zwartowo solar farm_1 -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9FBE2C5-F977-4037-912A-E38EF2065070}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B62B1A4-99B4-41DF-87F2-88DB11A9460B}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B554FDE1-8E2C-4F3C-915F-84F4ED03A47B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4325391-449B-4BA9-AC0C-AEF766F5DAF5}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB93C33-DF9A-44FB-B7B8-7DC60AE7F8E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BB4B19-2A63-430C-875D-F89B813596C4}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF56D5A-1CFF-4DB8-B2A8-E292F4A80F10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B3F273-C2CB-4B1F-A056-3C02A2651290}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C75F656F-D997-4EF7-AD18-DAC983DD47EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDE99544-45F6-4DFD-B762-AAC347A50C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DF54D25E-3258-44BF-A4AE-A2E297EDAFDC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8A533DDC-DD77-4E5B-89E3-F467FD8AE270}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2465,34 +2465,34 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2023) - 42_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Zwartowo solar farm_1 -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B62B1A4-99B4-41DF-87F2-88DB11A9460B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96454D97-01AA-4DAD-9729-B1E8F31347E9}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4325391-449B-4BA9-AC0C-AEF766F5DAF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A5E2EB-056B-443B-9CA5-2000B641C7DE}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BB4B19-2A63-430C-875D-F89B813596C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834D05E6-D3D0-4446-9055-0CDFE17B9B96}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B3F273-C2CB-4B1F-A056-3C02A2651290}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40F51AA-1C3D-48D2-9B17-35BCA2E259AE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDE99544-45F6-4DFD-B762-AAC347A50C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8555C798-41C4-4723-BA4D-DD1252943F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8A533DDC-DD77-4E5B-89E3-F467FD8AE270}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B5FC77EB-79E7-4329-915A-7A2EF5417F67}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2474,10 +2474,10 @@
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 38_Missing Solar Capacity -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96454D97-01AA-4DAD-9729-B1E8F31347E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D478C3-929E-47A0-B675-0E052DD0D855}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A5E2EB-056B-443B-9CA5-2000B641C7DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A699DC67-2D14-44F3-9C84-602E59E08277}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834D05E6-D3D0-4446-9055-0CDFE17B9B96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E728A59-AB64-4AF2-B659-7EF4585D923A}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40F51AA-1C3D-48D2-9B17-35BCA2E259AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239A190C-791B-4FFA-9847-073CCADDD7D4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8555C798-41C4-4723-BA4D-DD1252943F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07F3A598-F13C-4909-93BD-5374501B7439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B5FC77EB-79E7-4329-915A-7A2EF5417F67}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E18B42F3-F528-44DC-97E7-EF3DDF3DA633}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2465,15 +2465,15 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
@@ -2489,10 +2489,10 @@
     <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Zwartowo solar farm_1 -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D478C3-929E-47A0-B675-0E052DD0D855}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A63419-34D6-4CEF-AE9D-BC75E956AB29}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A699DC67-2D14-44F3-9C84-602E59E08277}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5AF7D0-C6C8-406E-983B-8DB97FF12EF7}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E728A59-AB64-4AF2-B659-7EF4585D923A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90066FF3-0A9A-491D-842D-6D912EE76278}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239A190C-791B-4FFA-9847-073CCADDD7D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC9747A-B994-4C49-8B4C-E607BC82BD3F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07F3A598-F13C-4909-93BD-5374501B7439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB5CAE71-C956-4C1F-B9C3-2BB460C7C953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E18B42F3-F528-44DC-97E7-EF3DDF3DA633}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AD43683A-091D-432B-BA5C-94A5D579193D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2468,10 +2468,13 @@
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2022) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2024) - 38_Missing Solar Capacity -- operating</t>
@@ -2480,19 +2483,16 @@
     <t>IRENA Gap - solar (2023) - 38_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2022) - 38_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2023) - 42_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 50_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 50_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Zwartowo solar farm_1 -- operating</t>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A63419-34D6-4CEF-AE9D-BC75E956AB29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3436B927-BC18-487F-BA8E-2501982B001C}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6284,7 +6284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5AF7D0-C6C8-406E-983B-8DB97FF12EF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C68F94-8562-423A-892E-D520ADA77ABF}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90066FF3-0A9A-491D-842D-6D912EE76278}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BDF134F-3E11-44A5-9700-85FFF51B6C6A}">
   <dimension ref="B9:Y731"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49655,7 +49655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC9747A-B994-4C49-8B4C-E607BC82BD3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9A33D2-4065-47C1-9290-AA60FB8C2F1D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
